--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536123_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536123_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>R. ISSANZA TSHUKA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.915</v>
+        <v>0.3034</v>
       </c>
       <c r="E7" t="n">
-        <v>0.915</v>
+        <v>4.7217</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-4.4183</v>
       </c>
       <c r="G7" t="n">
-        <v>0.915</v>
+        <v>-1.3473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3075</v>
+        <v>-0.1794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6075</v>
+        <v>-1.168</v>
       </c>
       <c r="J7" t="n">
-        <v>0.915</v>
+        <v>2.3147</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3075</v>
+        <v>1.4642</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6075</v>
+        <v>0.8505</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-3.662</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.6436</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-2.0185</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.1771</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.9083</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2688</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. ISSANZA TSHUKA</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3034</v>
+        <v>0.1927</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7217</v>
+        <v>2.678</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.4183</v>
+        <v>-2.4853</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3473</v>
+        <v>0.9697</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1794</v>
+        <v>0.2779</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.168</v>
+        <v>0.6918</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3147</v>
+        <v>3.5398</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4642</v>
+        <v>1.6527</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8505</v>
+        <v>1.8871</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.662</v>
+        <v>-2.5701</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6436</v>
+        <v>-1.3748</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0185</v>
+        <v>-1.1953</v>
       </c>
       <c r="P8" t="n">
-        <v>0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R8" t="n">
-        <v>0.195</v>
+        <v>0.7799</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1771</v>
+        <v>-0.7715</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9083</v>
+        <v>-0.132</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2688</v>
+        <v>-0.6395</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2786</v>
+        <v>1.1643</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4986</v>
+        <v>1.2201</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2201</v>
+        <v>-0.0557</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1927</v>
+        <v>-1.024</v>
       </c>
       <c r="E9" t="n">
-        <v>2.678</v>
+        <v>-1.5264</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4853</v>
+        <v>0.5024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9697</v>
+        <v>-1.9575</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2779</v>
+        <v>-0.475</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6918</v>
+        <v>-1.4825</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5398</v>
+        <v>-2.1605</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6527</v>
+        <v>-0.127</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8871</v>
+        <v>-2.0335</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5701</v>
+        <v>0.203</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3748</v>
+        <v>-0.348</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1953</v>
+        <v>0.551</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1699</v>
+        <v>-0.585</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7799</v>
+        <v>1.3649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7715</v>
+        <v>-0.0331</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.132</v>
+        <v>0.7539</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6395</v>
+        <v>-0.7869</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1643</v>
+        <v>1.5515</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2201</v>
+        <v>1.8301</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0557</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.024</v>
+        <v>-3.5999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5264</v>
+        <v>-1.1184</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5024</v>
+        <v>-2.4815</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9575</v>
+        <v>-2.5574</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.475</v>
+        <v>0.3394</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4825</v>
+        <v>-2.8968</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1605</v>
+        <v>-0.1974</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.127</v>
+        <v>1.0991</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0335</v>
+        <v>-1.2965</v>
       </c>
       <c r="M10" t="n">
-        <v>0.203</v>
+        <v>-2.36</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.348</v>
+        <v>-0.7598</v>
       </c>
       <c r="O10" t="n">
-        <v>0.551</v>
+        <v>-1.6003</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.585</v>
+        <v>-0.39</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3649</v>
+        <v>1.5599</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0331</v>
+        <v>0.2918</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7539</v>
+        <v>0.1402</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7869</v>
+        <v>0.1516</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5515</v>
+        <v>-0.9443</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8301</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2786</v>
+        <v>-1.8329</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>J. PLEASANT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5149</v>
+        <v>-6.0002</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0335</v>
+        <v>-4.3888</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4815</v>
+        <v>-1.6114</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4724</v>
+        <v>-6.0793</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0319</v>
+        <v>-3.6817</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.5043</v>
+        <v>-2.3976</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1124</v>
+        <v>-4.3966</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7916</v>
+        <v>-3.1976</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.904</v>
+        <v>-1.199</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.36</v>
+        <v>-1.6827</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7598</v>
+        <v>-0.4841</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6003</v>
+        <v>-1.1986</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.39</v>
+        <v>0.7799</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5599</v>
+        <v>0.7799</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2918</v>
+        <v>-0.9766</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1402</v>
+        <v>-0.2708</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1516</v>
+        <v>-0.7058</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9443</v>
+        <v>0.2758</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.2786</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8329</v>
+        <v>-0.0028</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PLEASANT</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,157 +1388,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0002</v>
+        <v>6.164500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3888</v>
+        <v>15.6282</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6114</v>
+        <v>-9.4634</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.0793</v>
+        <v>1.074399999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.6817</v>
+        <v>1.705499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3976</v>
+        <v>-0.6312000000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.3966</v>
+        <v>10.8511</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.1976</v>
+        <v>7.580200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.199</v>
+        <v>3.2708</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6827</v>
+        <v>-9.7765</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4841</v>
+        <v>-5.8747</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1986</v>
+        <v>-3.902</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7799</v>
+        <v>-0.9748999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-11.6993</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7799</v>
+        <v>10.7242</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9766</v>
+        <v>-0.3667999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2708</v>
+        <v>4.2086</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7058</v>
+        <v>-4.5753</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2758</v>
+        <v>6.431799999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2786</v>
+        <v>12.2676</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>play_by_play_2536123_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-5.8359</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. STARLABS MORÓN</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.164499999999999</v>
+        <v>3.7947</v>
       </c>
       <c r="E13" t="n">
-        <v>15.6281</v>
+        <v>4.7657</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.463400000000002</v>
+        <v>-0.971</v>
       </c>
       <c r="G13" t="n">
-        <v>1.074399999999999</v>
+        <v>3.5791</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7055</v>
+        <v>-2.7717</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6312000000000006</v>
+        <v>6.3507</v>
       </c>
       <c r="J13" t="n">
-        <v>10.8511</v>
+        <v>4.6063</v>
       </c>
       <c r="K13" t="n">
-        <v>7.580200000000001</v>
+        <v>-0.9179</v>
       </c>
       <c r="L13" t="n">
-        <v>3.270799999999999</v>
+        <v>5.5242</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.7765</v>
+        <v>-1.0272</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.8747</v>
+        <v>-1.8537</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.902</v>
+        <v>0.8265</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9748999999999999</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.6993</v>
+        <v>-2.9248</v>
       </c>
       <c r="R13" t="n">
-        <v>10.7242</v>
+        <v>1.5599</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3668000000000001</v>
+        <v>-0.459</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2086</v>
+        <v>0.6441</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.575299999999999</v>
+        <v>-1.1031</v>
       </c>
       <c r="V13" t="n">
-        <v>6.4318</v>
+        <v>2.0396</v>
       </c>
       <c r="W13" t="n">
-        <v>12.2676</v>
+        <v>2.4401</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.8359</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>-0.4006</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2536123_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>J. CHARLES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7947</v>
+        <v>2.0743</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7657</v>
+        <v>2.1407</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.971</v>
+        <v>-0.0664</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5791</v>
+        <v>1.019</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.7717</v>
+        <v>1.3331</v>
       </c>
       <c r="I14" t="n">
-        <v>6.3507</v>
+        <v>-0.3141</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6063</v>
+        <v>1.5571</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9179</v>
+        <v>1.4761</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5242</v>
+        <v>0.081</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0272</v>
+        <v>-0.5381</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8537</v>
+        <v>-0.143</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8265</v>
+        <v>-0.3951</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3649</v>
+        <v>0.7799</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9248</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5599</v>
+        <v>0.7799</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.459</v>
+        <v>-0.3347</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6441</v>
+        <v>0.305</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1031</v>
+        <v>-0.6397</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0396</v>
+        <v>0.61</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4401</v>
+        <v>0.2786</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4006</v>
+        <v>0.3315</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CHARLES</t>
+          <t>D. KROHNERT MOTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,40 +1633,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0743</v>
+        <v>1.7703</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1407</v>
+        <v>4.242</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0664</v>
+        <v>-2.4717</v>
       </c>
       <c r="G15" t="n">
-        <v>1.019</v>
+        <v>1.6237</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3331</v>
+        <v>1.8229</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3141</v>
+        <v>-0.1992</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5571</v>
+        <v>2.7012</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4761</v>
+        <v>1.9642</v>
       </c>
       <c r="L15" t="n">
-        <v>0.081</v>
+        <v>0.737</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5381</v>
+        <v>-1.0775</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.143</v>
+        <v>-0.1413</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3951</v>
+        <v>-0.9363</v>
       </c>
       <c r="P15" t="n">
         <v>0.7799</v>
@@ -1678,22 +1678,22 @@
         <v>0.7799</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3347</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.305</v>
+        <v>0.3207</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6397</v>
+        <v>-0.397</v>
       </c>
       <c r="V15" t="n">
-        <v>0.61</v>
+        <v>-0.5571</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2786</v>
+        <v>1.2201</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3315</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KROHNERT MOTO</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7703</v>
+        <v>1.3663</v>
       </c>
       <c r="E16" t="n">
-        <v>4.242</v>
+        <v>3.7267</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.4717</v>
+        <v>-2.3604</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6237</v>
+        <v>2.9657</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8229</v>
+        <v>1.4106</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1992</v>
+        <v>1.5551</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7012</v>
+        <v>3.9793</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9642</v>
+        <v>1.4847</v>
       </c>
       <c r="L16" t="n">
-        <v>0.737</v>
+        <v>2.4946</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0775</v>
+        <v>-1.0136</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1413</v>
+        <v>-0.0741</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9363</v>
+        <v>-0.9395</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7799</v>
+        <v>-0.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.6207</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3207</v>
+        <v>0.4438</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.397</v>
+        <v>0.1769</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5571</v>
+        <v>-1.8301</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2201</v>
+        <v>0.2786</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7772</v>
+        <v>-2.1086</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3663</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7267</v>
+        <v>1.6727</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3604</v>
+        <v>-0.9383</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9657</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4106</v>
+        <v>-0.2164</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5551</v>
+        <v>-0.4535</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9793</v>
+        <v>0.0731</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4847</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4946</v>
+        <v>0.081</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0136</v>
+        <v>-0.743</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0741</v>
+        <v>-0.2085</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9395</v>
+        <v>-0.5345</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.39</v>
+        <v>0.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.585</v>
+        <v>0.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6207</v>
+        <v>-0.0837</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4438</v>
+        <v>0.3796</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1769</v>
+        <v>-0.4633</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8301</v>
+        <v>1.0981</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2786</v>
+        <v>1.2201</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1086</v>
+        <v>-0.122</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7344000000000001</v>
+        <v>-0.4201</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6727</v>
+        <v>1.069</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9383</v>
+        <v>-1.4891</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.0694</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2164</v>
+        <v>1.0001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4535</v>
+        <v>-1.0695</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0731</v>
+        <v>1.7594</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.7598</v>
       </c>
       <c r="L18" t="n">
-        <v>0.081</v>
+        <v>-0.0005</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.743</v>
+        <v>-1.8288</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2085</v>
+        <v>-0.7598</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5345</v>
+        <v>-1.0691</v>
       </c>
       <c r="P18" t="n">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R18" t="n">
-        <v>0.39</v>
+        <v>1.5599</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0837</v>
+        <v>0.8772</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3796</v>
+        <v>0.7553</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4633</v>
+        <v>0.1219</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0981</v>
+        <v>-0.8379</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2201</v>
+        <v>0.5042</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.122</v>
+        <v>-1.3421</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3075</v>
+        <v>-1.3799</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3075</v>
+        <v>-1.1078</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0.2721</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3075</v>
+        <v>-1.3493</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3075</v>
+        <v>0.2369</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.5861</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3075</v>
+        <v>-0.9389</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3075</v>
+        <v>1.0621</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.001</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.4103</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.8252</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.4149</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.1894</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.5275</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.3381</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4201</v>
+        <v>-1.99</v>
       </c>
       <c r="E20" t="n">
-        <v>1.069</v>
+        <v>-1.4072</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4891</v>
+        <v>-0.5828</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0694</v>
+        <v>-0.803</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0001</v>
+        <v>-0.3428</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0695</v>
+        <v>-0.4601</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7594</v>
+        <v>-0.1895</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7598</v>
+        <v>0.41</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0005</v>
+        <v>-0.5995</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8288</v>
+        <v>-0.6135</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7598</v>
+        <v>-0.7529</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0691</v>
+        <v>0.1394</v>
       </c>
       <c r="P20" t="n">
         <v>-0.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5599</v>
+        <v>0.585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8772</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7553</v>
+        <v>0.4201</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1219</v>
+        <v>0.4563</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8379</v>
+        <v>-1.6735</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5042</v>
+        <v>-0.6629</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3421</v>
+        <v>-1.0106</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3799</v>
+        <v>-2.1379</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1078</v>
+        <v>-1.9377</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2721</v>
+        <v>-0.2002</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3493</v>
+        <v>-1.1541</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2369</v>
+        <v>-1.131</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5861</v>
+        <v>-0.0231</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9389</v>
+        <v>-0.611</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0621</v>
+        <v>-0.578</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.001</v>
+        <v>-0.0329</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4103</v>
+        <v>-0.5431</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8252</v>
+        <v>-0.553</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4149</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.39</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3649</v>
+        <v>0.9749</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1894</v>
+        <v>-0.5833</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5275</v>
+        <v>-0.3519</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3381</v>
+        <v>-0.2314</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.61</v>
+        <v>-0.4006</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.4006</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.99</v>
+        <v>-4.0458</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4072</v>
+        <v>-0.5764</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5828</v>
+        <v>-3.4694</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.803</v>
+        <v>-2.619</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3428</v>
+        <v>-2.0991</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4601</v>
+        <v>-0.5199</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1895</v>
+        <v>-0.7164</v>
       </c>
       <c r="K22" t="n">
-        <v>0.41</v>
+        <v>-0.9999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5995</v>
+        <v>0.2835</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6135</v>
+        <v>-1.9026</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7529</v>
+        <v>-1.0991</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1394</v>
+        <v>-0.8034</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.39</v>
+        <v>0.195</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R22" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8183</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4201</v>
+        <v>0.8364</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4563</v>
+        <v>-0.0181</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6735</v>
+        <v>-2.4401</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6629</v>
+        <v>0.2786</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0106</v>
+        <v>-2.7187</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>P. SUAREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1379</v>
+        <v>-5.2399</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9377</v>
+        <v>-3.0222</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2002</v>
+        <v>-2.2177</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1541</v>
+        <v>-3.5973</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.131</v>
+        <v>-0.9482</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0231</v>
+        <v>-2.6491</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.611</v>
+        <v>-2.444</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.578</v>
+        <v>0.2216</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0329</v>
+        <v>-2.6655</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5431</v>
+        <v>-1.1533</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.553</v>
+        <v>-1.1698</v>
       </c>
       <c r="O23" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>0.9749</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9749</v>
+        <v>1.9499</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5833</v>
+        <v>-0.7874</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3519</v>
+        <v>0.3967</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2314</v>
+        <v>-1.1841</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4006</v>
+        <v>-1.8301</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4006</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,235 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3534</v>
+        <v>-5.4736</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8839</v>
+        <v>9.565500000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4694</v>
+        <v>-15.0391</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9265</v>
+        <v>-1.0745</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4066</v>
+        <v>-1.7056</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5199</v>
+        <v>0.6311999999999998</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0239</v>
+        <v>9.776600000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3075</v>
+        <v>5.8748</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2835</v>
+        <v>3.901900000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9026</v>
+        <v>-10.851</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0991</v>
+        <v>-7.580399999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8034</v>
+        <v>-3.270699999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.195</v>
+        <v>0.9748000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9749</v>
+        <v>-10.7241</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1699</v>
+        <v>11.6992</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8183</v>
+        <v>1.0577</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8364</v>
+        <v>4.6773</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0181</v>
+        <v>-3.619699999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4401</v>
+        <v>-6.431699999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2786</v>
+        <v>5.835999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.7187</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536123_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P. SUAREZ CUSTODIO</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-5.2399</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-3.0222</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2.2177</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-3.5973</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.9482</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-2.6491</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-2.444</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.2216</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-2.6655</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-1.1533</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-1.1698</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.9749</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-0.9749</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.9499</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-0.7874</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.3967</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-1.1841</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-1.8301</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-1.8301</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536123_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-5.473700000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>9.565500000000002</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-15.0391</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-1.0745</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1.7056</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.6312000000000006</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9.776600000000002</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.8747</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3.9019</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-10.851</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-7.580399999999999</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-3.270699999999999</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.9748000000000001</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-10.7241</v>
-      </c>
-      <c r="R26" t="n">
-        <v>11.6992</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.0577</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4.6773</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-3.619699999999999</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-6.431699999999999</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5.835999999999999</v>
-      </c>
-      <c r="X26" t="n">
         <v>-12.2676</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
